--- a/database/event/5728/event_5728_evp_summary.xlsx
+++ b/database/event/5728/event_5728_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>3.3212</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E2" t="n">
         <v>6.4635</v>
@@ -514,10 +514,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>8.6951</v>
+        <v>8.9312</v>
       </c>
       <c r="I2" t="n">
-        <v>9.1508</v>
+        <v>9.793799999999999</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>9.1508</v>
+        <v>9.793799999999999</v>
       </c>
       <c r="N2" t="n">
         <v>403</v>
@@ -538,93 +538,93 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.0087</v>
+        <v>5.2739</v>
       </c>
       <c r="C3" t="n">
-        <v>2.5737</v>
+        <v>2.71</v>
       </c>
       <c r="D3" t="n">
-        <v>1.602</v>
+        <v>1.6572</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0087</v>
+        <v>5.2739</v>
       </c>
       <c r="F3" t="n">
-        <v>5.0087</v>
+        <v>5.2739</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.5506</v>
+        <v>5.9664</v>
       </c>
       <c r="I3" t="n">
-        <v>5.6546</v>
+        <v>6.3269</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>210</v>
+        <v>296</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>5.6546</v>
+        <v>6.3269</v>
       </c>
       <c r="N3" t="n">
-        <v>210</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.918</v>
+        <v>4.9562</v>
       </c>
       <c r="C4" t="n">
-        <v>2.5271</v>
+        <v>2.5467</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5654</v>
+        <v>1.5306</v>
       </c>
       <c r="E4" t="n">
-        <v>4.918</v>
+        <v>4.9562</v>
       </c>
       <c r="F4" t="n">
-        <v>4.918</v>
+        <v>4.9562</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>5.4084</v>
+        <v>5.4682</v>
       </c>
       <c r="I4" t="n">
-        <v>5.5871</v>
+        <v>5.6546</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>296</v>
+        <v>210</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5.5871</v>
+        <v>5.6546</v>
       </c>
       <c r="N4" t="n">
-        <v>296</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5">
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2586</v>
+        <v>4.1827</v>
       </c>
       <c r="C5" t="n">
-        <v>2.1883</v>
+        <v>2.1493</v>
       </c>
       <c r="D5" t="n">
-        <v>1.299</v>
+        <v>1.2225</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2586</v>
+        <v>4.1827</v>
       </c>
       <c r="F5" t="n">
-        <v>4.2586</v>
+        <v>4.1827</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3744</v>
+        <v>4.2554</v>
       </c>
       <c r="I5" t="n">
-        <v>4.54</v>
+        <v>4.5505</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.54</v>
+        <v>4.5505</v>
       </c>
       <c r="N5" t="n">
         <v>338</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1234</v>
+        <v>4.1636</v>
       </c>
       <c r="C6" t="n">
-        <v>2.1188</v>
+        <v>2.1395</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2444</v>
+        <v>1.2149</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1234</v>
+        <v>4.1636</v>
       </c>
       <c r="F6" t="n">
-        <v>4.1234</v>
+        <v>4.1636</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1624</v>
+        <v>4.2255</v>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>4.4808</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3</v>
+        <v>4.4808</v>
       </c>
       <c r="N6" t="n">
         <v>296</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1043</v>
+        <v>4.145</v>
       </c>
       <c r="C7" t="n">
-        <v>2.109</v>
+        <v>2.1299</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2367</v>
+        <v>1.2075</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1043</v>
+        <v>4.145</v>
       </c>
       <c r="F7" t="n">
-        <v>4.1043</v>
+        <v>4.145</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1325</v>
+        <v>4.1963</v>
       </c>
       <c r="I7" t="n">
-        <v>4.269</v>
+        <v>4.4499</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.269</v>
+        <v>4.4499</v>
       </c>
       <c r="N7" t="n">
         <v>296</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7226</v>
+        <v>3.6264</v>
       </c>
       <c r="C8" t="n">
-        <v>1.9128</v>
+        <v>1.8634</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0825</v>
+        <v>1.0008</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7226</v>
+        <v>3.6264</v>
       </c>
       <c r="F8" t="n">
-        <v>3.7226</v>
+        <v>3.6264</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7226</v>
+        <v>3.6264</v>
       </c>
       <c r="I8" t="n">
         <v>3.8456</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5972</v>
+        <v>3.4913</v>
       </c>
       <c r="C9" t="n">
-        <v>1.8484</v>
+        <v>1.794</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0318</v>
+        <v>0.947</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5972</v>
+        <v>3.4913</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5972</v>
+        <v>3.4913</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5972</v>
+        <v>3.4913</v>
       </c>
       <c r="I9" t="n">
         <v>3.7334</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4017</v>
+        <v>3.3276</v>
       </c>
       <c r="C10" t="n">
-        <v>1.748</v>
+        <v>1.7099</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9528</v>
+        <v>0.8818</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4017</v>
+        <v>3.3276</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4017</v>
+        <v>3.3276</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4017</v>
+        <v>3.3276</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4978</v>
+        <v>3.4992</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4978</v>
+        <v>3.4992</v>
       </c>
       <c r="N10" t="n">
         <v>204</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8553</v>
+        <v>2.7919</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4672</v>
+        <v>1.4346</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7321</v>
+        <v>0.6684</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8553</v>
+        <v>2.7919</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8553</v>
+        <v>2.7919</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8553</v>
+        <v>2.7919</v>
       </c>
       <c r="I11" t="n">
         <v>2.9359</v>
@@ -952,32 +952,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5518</v>
+        <v>2.7537</v>
       </c>
       <c r="C12" t="n">
-        <v>1.3112</v>
+        <v>1.415</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6095</v>
+        <v>0.6532</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5518</v>
+        <v>2.7537</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5518</v>
+        <v>2.7537</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5518</v>
+        <v>2.7537</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6239</v>
+        <v>2.8957</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.6239</v>
+        <v>2.8957</v>
       </c>
       <c r="N12" t="n">
         <v>204</v>
@@ -998,32 +998,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.533</v>
+        <v>2.4953</v>
       </c>
       <c r="C13" t="n">
-        <v>1.3016</v>
+        <v>1.2822</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6019</v>
+        <v>0.5502</v>
       </c>
       <c r="E13" t="n">
-        <v>2.533</v>
+        <v>2.4953</v>
       </c>
       <c r="F13" t="n">
-        <v>2.533</v>
+        <v>2.4953</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.533</v>
+        <v>2.4953</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6045</v>
+        <v>2.6239</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6045</v>
+        <v>2.6239</v>
       </c>
       <c r="N13" t="n">
         <v>204</v>
@@ -1044,507 +1044,507 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4049</v>
+        <v>2.3784</v>
       </c>
       <c r="C14" t="n">
-        <v>1.2357</v>
+        <v>1.2221</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5502</v>
+        <v>0.5036</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4049</v>
+        <v>2.3784</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4049</v>
+        <v>2.3784</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4049</v>
+        <v>2.3784</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4728</v>
+        <v>2.439</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4728</v>
+        <v>2.439</v>
       </c>
       <c r="N14" t="n">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2345</v>
+        <v>2.3515</v>
       </c>
       <c r="C15" t="n">
-        <v>1.1482</v>
+        <v>1.2083</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4813</v>
+        <v>0.4929</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2345</v>
+        <v>2.3515</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2345</v>
+        <v>2.3515</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2345</v>
+        <v>2.3515</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3516</v>
+        <v>2.4728</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>403</v>
+        <v>204</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3516</v>
+        <v>2.4728</v>
       </c>
       <c r="N15" t="n">
-        <v>403</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1996</v>
+        <v>2.3113</v>
       </c>
       <c r="C16" t="n">
-        <v>1.1303</v>
+        <v>1.1877</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4672</v>
+        <v>0.4769</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1996</v>
+        <v>2.3113</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1996</v>
+        <v>2.3113</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1996</v>
+        <v>2.3113</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3149</v>
+        <v>2.3901</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>403</v>
+        <v>212</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.3149</v>
+        <v>2.3901</v>
       </c>
       <c r="N16" t="n">
-        <v>403</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.109</v>
+        <v>2.1445</v>
       </c>
       <c r="C17" t="n">
-        <v>1.0837</v>
+        <v>1.1019</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4306</v>
+        <v>0.4105</v>
       </c>
       <c r="E17" t="n">
-        <v>2.109</v>
+        <v>2.1445</v>
       </c>
       <c r="F17" t="n">
-        <v>2.109</v>
+        <v>2.1445</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.109</v>
+        <v>2.1445</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1787</v>
+        <v>2.3516</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>296</v>
+        <v>403</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.1787</v>
+        <v>2.3516</v>
       </c>
       <c r="N17" t="n">
-        <v>296</v>
+        <v>403</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.0355</v>
+        <v>2.14</v>
       </c>
       <c r="C18" t="n">
-        <v>1.0459</v>
+        <v>1.0996</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4009</v>
+        <v>0.4087</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0355</v>
+        <v>2.14</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0355</v>
+        <v>2.14</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0355</v>
+        <v>2.14</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0641</v>
+        <v>2.1762</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.0641</v>
+        <v>2.1762</v>
       </c>
       <c r="N18" t="n">
-        <v>184</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.888</v>
+        <v>2.111</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9701</v>
+        <v>1.0847</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3413</v>
+        <v>0.3971</v>
       </c>
       <c r="E19" t="n">
-        <v>1.888</v>
+        <v>2.111</v>
       </c>
       <c r="F19" t="n">
-        <v>1.888</v>
+        <v>2.111</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.888</v>
+        <v>2.111</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9057</v>
+        <v>2.3149</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>172</v>
+        <v>403</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9057</v>
+        <v>2.3149</v>
       </c>
       <c r="N19" t="n">
-        <v>172</v>
+        <v>403</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.8228</v>
+        <v>2.0546</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9366</v>
+        <v>1.0557</v>
       </c>
       <c r="D20" t="n">
-        <v>0.315</v>
+        <v>0.3746</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8228</v>
+        <v>2.0546</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8228</v>
+        <v>2.0546</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8228</v>
+        <v>2.0546</v>
       </c>
       <c r="I20" t="n">
-        <v>1.857</v>
+        <v>2.1787</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>212</v>
+        <v>296</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.857</v>
+        <v>2.1787</v>
       </c>
       <c r="N20" t="n">
-        <v>212</v>
+        <v>296</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.6058</v>
+        <v>1.7317</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8250999999999999</v>
+        <v>0.8898</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2273</v>
+        <v>0.246</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6058</v>
+        <v>1.7317</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6058</v>
+        <v>1.7317</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6058</v>
+        <v>1.7317</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6589</v>
+        <v>1.7463</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>288</v>
+        <v>156</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.6589</v>
+        <v>1.7463</v>
       </c>
       <c r="N21" t="n">
-        <v>288</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bubzkji</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.4674</v>
+        <v>1.5644</v>
       </c>
       <c r="C22" t="n">
-        <v>0.754</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1714</v>
+        <v>0.1793</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4674</v>
+        <v>1.5644</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4674</v>
+        <v>1.5644</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4674</v>
+        <v>1.5644</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4949</v>
+        <v>1.6589</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>212</v>
+        <v>288</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4949</v>
+        <v>1.6589</v>
       </c>
       <c r="N22" t="n">
-        <v>212</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>Bubzkji</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.4591</v>
+        <v>1.5219</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7498</v>
+        <v>0.782</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1681</v>
+        <v>0.1624</v>
       </c>
       <c r="E23" t="n">
-        <v>1.4591</v>
+        <v>1.5219</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4591</v>
+        <v>1.5219</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.4591</v>
+        <v>1.5219</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4727</v>
+        <v>1.5737</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>164</v>
+        <v>212</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.4727</v>
+        <v>1.5737</v>
       </c>
       <c r="N23" t="n">
-        <v>164</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.3195</v>
+        <v>1.4482</v>
       </c>
       <c r="C24" t="n">
-        <v>0.678</v>
+        <v>0.7442</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1117</v>
+        <v>0.1331</v>
       </c>
       <c r="E24" t="n">
-        <v>1.3195</v>
+        <v>1.4482</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3195</v>
+        <v>1.4482</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3195</v>
+        <v>1.4482</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3256</v>
+        <v>1.4727</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.3256</v>
+        <v>1.4727</v>
       </c>
       <c r="N24" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25">
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.3058</v>
+        <v>1.272</v>
       </c>
       <c r="C25" t="n">
-        <v>0.671</v>
+        <v>0.6536</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1062</v>
+        <v>0.0629</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3058</v>
+        <v>1.272</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3058</v>
+        <v>1.272</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.3058</v>
+        <v>1.272</v>
       </c>
       <c r="I25" t="n">
         <v>1.3489</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.1787</v>
+        <v>1.1743</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6057</v>
+        <v>0.6034</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0548</v>
+        <v>0.0239</v>
       </c>
       <c r="E26" t="n">
-        <v>1.1787</v>
+        <v>1.1743</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1787</v>
+        <v>1.1743</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.1787</v>
+        <v>1.1743</v>
       </c>
       <c r="I26" t="n">
         <v>1.1842</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.1655</v>
+        <v>1.1482</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5989</v>
+        <v>0.59</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0495</v>
+        <v>0.0135</v>
       </c>
       <c r="E27" t="n">
-        <v>1.1655</v>
+        <v>1.1482</v>
       </c>
       <c r="F27" t="n">
-        <v>1.1655</v>
+        <v>1.1482</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.1655</v>
+        <v>1.1482</v>
       </c>
       <c r="I27" t="n">
         <v>1.1874</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.1015</v>
+        <v>1.0893</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5597</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0236</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>1.1015</v>
+        <v>1.0893</v>
       </c>
       <c r="F28" t="n">
-        <v>1.1015</v>
+        <v>1.0893</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.1015</v>
+        <v>1.0893</v>
       </c>
       <c r="I28" t="n">
         <v>1.117</v>
@@ -1734,170 +1734,170 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9176</v>
+        <v>0.9396</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4715</v>
+        <v>0.4828</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0507</v>
+        <v>-0.0696</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9176</v>
+        <v>0.9396</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9176</v>
+        <v>0.9396</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9176</v>
+        <v>0.9396</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9262</v>
+        <v>0.9475</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>164</v>
+        <v>126</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9262</v>
+        <v>0.9475</v>
       </c>
       <c r="N29" t="n">
-        <v>164</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7451</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3829</v>
+        <v>0.468</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1204</v>
+        <v>-0.081</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7451</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7451</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7451</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7591</v>
+        <v>0.9262</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>210</v>
+        <v>164</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.7591</v>
+        <v>0.9262</v>
       </c>
       <c r="N30" t="n">
-        <v>210</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7284</v>
+        <v>0.7341</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3743</v>
+        <v>0.3772</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1271</v>
+        <v>-0.1514</v>
       </c>
       <c r="E31" t="n">
-        <v>0.7284</v>
+        <v>0.7341</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7284</v>
+        <v>0.7341</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.7284</v>
+        <v>0.7341</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7352</v>
+        <v>0.7591</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7352</v>
+        <v>0.7591</v>
       </c>
       <c r="N31" t="n">
-        <v>172</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6964</v>
+        <v>0.723</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3578</v>
+        <v>0.3715</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.14</v>
+        <v>-0.1559</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6964</v>
+        <v>0.723</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6964</v>
+        <v>0.723</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6964</v>
+        <v>0.723</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7029</v>
+        <v>0.7352</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.7029</v>
+        <v>0.7352</v>
       </c>
       <c r="N32" t="n">
         <v>172</v>
@@ -1918,400 +1918,400 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.555</v>
+        <v>0.6912</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2852</v>
+        <v>0.3552</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1972</v>
+        <v>-0.1685</v>
       </c>
       <c r="E33" t="n">
-        <v>0.555</v>
+        <v>0.6912</v>
       </c>
       <c r="F33" t="n">
-        <v>0.555</v>
+        <v>0.6912</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.555</v>
+        <v>0.6912</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5576</v>
+        <v>0.7029</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.5576</v>
+        <v>0.7029</v>
       </c>
       <c r="N33" t="n">
-        <v>109</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bubble</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5411</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>0.278</v>
+        <v>0.2841</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2028</v>
+        <v>-0.2236</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5411</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5411</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5411</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5436</v>
+        <v>0.5576</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.5436</v>
+        <v>0.5576</v>
       </c>
       <c r="N34" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>bubble</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4886</v>
+        <v>0.5391</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2511</v>
+        <v>0.277</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.224</v>
+        <v>-0.2291</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4886</v>
+        <v>0.5391</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4886</v>
+        <v>0.5391</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.4886</v>
+        <v>0.5391</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4932</v>
+        <v>0.5436</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>172</v>
+        <v>104</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.4932</v>
+        <v>0.5436</v>
       </c>
       <c r="N35" t="n">
-        <v>172</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.377</v>
+        <v>0.485</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1937</v>
+        <v>0.2492</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2691</v>
+        <v>-0.2507</v>
       </c>
       <c r="E36" t="n">
-        <v>0.377</v>
+        <v>0.485</v>
       </c>
       <c r="F36" t="n">
-        <v>0.377</v>
+        <v>0.485</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.377</v>
+        <v>0.485</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3841</v>
+        <v>0.4932</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.3841</v>
+        <v>0.4932</v>
       </c>
       <c r="N36" t="n">
-        <v>210</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bymas</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3429</v>
+        <v>0.3714</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1762</v>
+        <v>0.1908</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2828</v>
+        <v>-0.2959</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3429</v>
+        <v>0.3714</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3429</v>
+        <v>0.3714</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3429</v>
+        <v>0.3714</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3461</v>
+        <v>0.3841</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>164</v>
+        <v>210</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.3461</v>
+        <v>0.3841</v>
       </c>
       <c r="N37" t="n">
-        <v>164</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.3224</v>
+        <v>0.3559</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1657</v>
+        <v>0.1829</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2911</v>
+        <v>-0.3021</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3224</v>
+        <v>0.3559</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3224</v>
+        <v>0.3559</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3224</v>
+        <v>0.3559</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3254</v>
+        <v>0.368</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>164</v>
+        <v>212</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.3254</v>
+        <v>0.368</v>
       </c>
       <c r="N38" t="n">
-        <v>164</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Bymas</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.3043</v>
+        <v>0.3403</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1564</v>
+        <v>0.1749</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2984</v>
+        <v>-0.3083</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3043</v>
+        <v>0.3403</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3043</v>
+        <v>0.3403</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3043</v>
+        <v>0.3403</v>
       </c>
       <c r="I39" t="n">
-        <v>0.31</v>
+        <v>0.3461</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>212</v>
+        <v>164</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.31</v>
+        <v>0.3461</v>
       </c>
       <c r="N39" t="n">
-        <v>212</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.2707</v>
+        <v>0.32</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1391</v>
+        <v>0.1644</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.312</v>
+        <v>-0.3164</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2707</v>
+        <v>0.32</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2707</v>
+        <v>0.32</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2707</v>
+        <v>0.32</v>
       </c>
       <c r="I40" t="n">
-        <v>0.272</v>
+        <v>0.3254</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>109</v>
+        <v>164</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.272</v>
+        <v>0.3254</v>
       </c>
       <c r="N40" t="n">
-        <v>109</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.2654</v>
+        <v>0.2998</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1364</v>
+        <v>0.1541</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3141</v>
+        <v>-0.3245</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2654</v>
+        <v>0.2998</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2654</v>
+        <v>0.2998</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2654</v>
+        <v>0.2998</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2703</v>
+        <v>0.31</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.2703</v>
+        <v>0.31</v>
       </c>
       <c r="N41" t="n">
         <v>212</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.2377</v>
+        <v>0.2939</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1221</v>
+        <v>0.151</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3253</v>
+        <v>-0.3268</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2377</v>
+        <v>0.2939</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2377</v>
+        <v>0.2939</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2377</v>
+        <v>0.2939</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2455</v>
+        <v>0.3117</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2455</v>
+        <v>0.3117</v>
       </c>
       <c r="N42" t="n">
         <v>296</v>
@@ -2378,93 +2378,93 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.1858</v>
+        <v>0.2697</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0955</v>
+        <v>0.1386</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3463</v>
+        <v>-0.3365</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1858</v>
+        <v>0.2697</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1858</v>
+        <v>0.2697</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1858</v>
+        <v>0.2697</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1875</v>
+        <v>0.272</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>172</v>
+        <v>109</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.1875</v>
+        <v>0.272</v>
       </c>
       <c r="N43" t="n">
-        <v>172</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.1802</v>
+        <v>0.1844</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0926</v>
+        <v>0.0948</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3486</v>
+        <v>-0.3704</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1802</v>
+        <v>0.1844</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1802</v>
+        <v>0.1844</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1802</v>
+        <v>0.1844</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1811</v>
+        <v>0.1875</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>126</v>
+        <v>172</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1811</v>
+        <v>0.1875</v>
       </c>
       <c r="N44" t="n">
-        <v>126</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45">
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.162</v>
+        <v>0.1555</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0832</v>
+        <v>0.0799</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3559</v>
+        <v>-0.382</v>
       </c>
       <c r="E45" t="n">
-        <v>0.162</v>
+        <v>0.1555</v>
       </c>
       <c r="F45" t="n">
-        <v>0.162</v>
+        <v>0.1555</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.162</v>
+        <v>0.1555</v>
       </c>
       <c r="I45" t="n">
         <v>0.1705</v>
@@ -2516,277 +2516,277 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.0535</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0275</v>
+        <v>0.0485</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3997</v>
+        <v>-0.4063</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0535</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0535</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0535</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0537</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>96</v>
+        <v>184</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.0537</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>96</v>
+        <v>184</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.0251</v>
+        <v>0.0533</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0129</v>
+        <v>0.0274</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4315</v>
+        <v>-0.4227</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.0251</v>
+        <v>0.0533</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.0251</v>
+        <v>0.0533</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.0251</v>
+        <v>0.0533</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0261</v>
+        <v>0.0537</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>338</v>
+        <v>96</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.0261</v>
+        <v>0.0537</v>
       </c>
       <c r="N47" t="n">
-        <v>338</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.0259</v>
+        <v>-0.0244</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0133</v>
+        <v>-0.0125</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4318</v>
+        <v>-0.4536</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0259</v>
+        <v>-0.0244</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.0259</v>
+        <v>-0.0244</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.0259</v>
+        <v>-0.0244</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0259</v>
+        <v>-0.0261</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>78</v>
+        <v>338</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.0259</v>
+        <v>-0.0261</v>
       </c>
       <c r="N48" t="n">
-        <v>78</v>
+        <v>338</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.0305</v>
+        <v>-0.0259</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0157</v>
+        <v>-0.0133</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4337</v>
+        <v>-0.4542</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.0305</v>
+        <v>-0.0259</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.0305</v>
+        <v>-0.0259</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.0305</v>
+        <v>-0.0259</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0317</v>
+        <v>-0.0259</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>338</v>
+        <v>78</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.0317</v>
+        <v>-0.0259</v>
       </c>
       <c r="N49" t="n">
-        <v>338</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.0409</v>
+        <v>-0.0296</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.021</v>
+        <v>-0.0152</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4379</v>
+        <v>-0.4557</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.0409</v>
+        <v>-0.0296</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.0409</v>
+        <v>-0.0296</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.0409</v>
+        <v>-0.0296</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0423</v>
+        <v>-0.0317</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>288</v>
+        <v>338</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.0423</v>
+        <v>-0.0317</v>
       </c>
       <c r="N50" t="n">
-        <v>288</v>
+        <v>338</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.1417</v>
+        <v>-0.0399</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0728</v>
+        <v>-0.0205</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4786</v>
+        <v>-0.4598</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.1417</v>
+        <v>-0.0399</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.1417</v>
+        <v>-0.0399</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.1417</v>
+        <v>-0.0399</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1437</v>
+        <v>-0.0423</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>184</v>
+        <v>288</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.1437</v>
+        <v>-0.0423</v>
       </c>
       <c r="N51" t="n">
-        <v>184</v>
+        <v>288</v>
       </c>
     </row>
     <row r="52">
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.2542</v>
+        <v>-0.2533</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1306</v>
+        <v>-0.1302</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5241</v>
+        <v>-0.5448</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.2542</v>
+        <v>-0.2533</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.2542</v>
+        <v>-0.2533</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.2542</v>
+        <v>-0.2533</v>
       </c>
       <c r="I52" t="n">
         <v>-0.2554</v>
@@ -2848,7 +2848,7 @@
         <v>-0.1343</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5269</v>
+        <v>-0.548</v>
       </c>
       <c r="E53" t="n">
         <v>-0.2613</v>
@@ -2888,25 +2888,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.2681</v>
+        <v>-0.2671</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1378</v>
+        <v>-0.1372</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.5503</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.2681</v>
+        <v>-0.2671</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.2681</v>
+        <v>-0.2671</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.2681</v>
+        <v>-0.2671</v>
       </c>
       <c r="I54" t="n">
         <v>-0.2693</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.2731</v>
+        <v>-0.2721</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1403</v>
+        <v>-0.1398</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5317</v>
+        <v>-0.5523</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.2731</v>
+        <v>-0.2721</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.2731</v>
+        <v>-0.2721</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.2731</v>
+        <v>-0.2721</v>
       </c>
       <c r="I55" t="n">
         <v>-0.2744</v>
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.3047</v>
+        <v>-0.3035</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1566</v>
+        <v>-0.156</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5445</v>
+        <v>-0.5648</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.3047</v>
+        <v>-0.3035</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.3047</v>
+        <v>-0.3035</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.3047</v>
+        <v>-0.3035</v>
       </c>
       <c r="I56" t="n">
         <v>-0.3061</v>
@@ -3026,25 +3026,25 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.3921</v>
+        <v>-0.3906</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.2015</v>
+        <v>-0.2007</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5798</v>
+        <v>-0.5995</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.3921</v>
+        <v>-0.3906</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.3921</v>
+        <v>-0.3906</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.3921</v>
+        <v>-0.3906</v>
       </c>
       <c r="I57" t="n">
         <v>-0.3939</v>
@@ -3068,553 +3068,553 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>hardzao</t>
+          <t>k1to</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.4363</v>
+        <v>-0.394</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2242</v>
+        <v>-0.2025</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5976</v>
+        <v>-0.6009</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.4363</v>
+        <v>-0.394</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.4363</v>
+        <v>-0.394</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.4363</v>
+        <v>-0.394</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.4363</v>
+        <v>-0.3973</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.4363</v>
+        <v>-0.3973</v>
       </c>
       <c r="N58" t="n">
-        <v>78</v>
+        <v>126</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>v1c7oR</t>
+          <t>hardzao</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.6039</v>
+        <v>-0.4363</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.3103</v>
+        <v>-0.2242</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6653</v>
+        <v>-0.6177</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.6039</v>
+        <v>-0.4363</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.6039</v>
+        <v>-0.4363</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.6039</v>
+        <v>-0.4363</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.6067</v>
+        <v>-0.4363</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.6067</v>
+        <v>-0.4363</v>
       </c>
       <c r="N59" t="n">
-        <v>104</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>v1c7oR</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.7059</v>
+        <v>-0.6016</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.3627</v>
+        <v>-0.3091</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7065</v>
+        <v>-0.6836</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.7059</v>
+        <v>-0.6016</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.7059</v>
+        <v>-0.6016</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.7059</v>
+        <v>-0.6016</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.7092000000000001</v>
+        <v>-0.6067</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.7092000000000001</v>
+        <v>-0.6067</v>
       </c>
       <c r="N60" t="n">
-        <v>156</v>
+        <v>104</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.8373</v>
+        <v>-0.7033</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.4302</v>
+        <v>-0.3614</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-0.7241</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.8373</v>
+        <v>-0.7033</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.8373</v>
+        <v>-0.7033</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.8373</v>
+        <v>-0.7033</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.8373</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.8373</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="N61" t="n">
-        <v>78</v>
+        <v>156</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>poizon</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.8759</v>
+        <v>-0.8373</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.4501</v>
+        <v>-0.4302</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7752</v>
+        <v>-0.7775</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.8759</v>
+        <v>-0.8373</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.8759</v>
+        <v>-0.8373</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.8759</v>
+        <v>-0.8373</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.88</v>
+        <v>-0.8373</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.88</v>
+        <v>-0.8373</v>
       </c>
       <c r="N62" t="n">
-        <v>156</v>
+        <v>78</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>poizon</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.8946</v>
+        <v>-0.8727</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.4597</v>
+        <v>-0.4484</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7828000000000001</v>
+        <v>-0.7916</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.8946</v>
+        <v>-0.8727</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.8946</v>
+        <v>-0.8727</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.8946</v>
+        <v>-0.8727</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.9114</v>
+        <v>-0.88</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>212</v>
+        <v>156</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.9114</v>
+        <v>-0.88</v>
       </c>
       <c r="N63" t="n">
-        <v>212</v>
+        <v>156</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.9207</v>
+        <v>-0.8814</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.4731</v>
+        <v>-0.4529</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7933</v>
+        <v>-0.7951</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.9207</v>
+        <v>-0.8814</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.9207</v>
+        <v>-0.8814</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.9207</v>
+        <v>-0.8814</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.925</v>
+        <v>-0.9114</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.925</v>
+        <v>-0.9114</v>
       </c>
       <c r="N64" t="n">
-        <v>126</v>
+        <v>212</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.9555</v>
+        <v>-0.9173</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.491</v>
+        <v>-0.4714</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8074</v>
+        <v>-0.8094</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.9555</v>
+        <v>-0.9173</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.9555</v>
+        <v>-0.9173</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.9555</v>
+        <v>-0.9173</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.9644</v>
+        <v>-0.925</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>164</v>
+        <v>126</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.9644</v>
+        <v>-0.925</v>
       </c>
       <c r="N65" t="n">
-        <v>164</v>
+        <v>126</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.9673</v>
+        <v>-0.9484</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.497</v>
+        <v>-0.4873</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8121</v>
+        <v>-0.8218</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.9673</v>
+        <v>-0.9484</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.9673</v>
+        <v>-0.9484</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.9673</v>
+        <v>-0.9484</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.9718</v>
+        <v>-0.9644</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.9718</v>
+        <v>-0.9644</v>
       </c>
       <c r="N66" t="n">
-        <v>126</v>
+        <v>164</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MarKE</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.0202</v>
+        <v>-0.9637</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.5242</v>
+        <v>-0.4952</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8335</v>
+        <v>-0.8278</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.0202</v>
+        <v>-0.9637</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.0202</v>
+        <v>-0.9637</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-1.0202</v>
+        <v>-0.9637</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0249</v>
+        <v>-0.9718</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-1.0249</v>
+        <v>-0.9718</v>
       </c>
       <c r="N67" t="n">
-        <v>96</v>
+        <v>126</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>mar</t>
+          <t>MarKE</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.0975</v>
+        <v>-1.0163</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5639</v>
+        <v>-0.5222</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8647</v>
+        <v>-0.8488</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.0975</v>
+        <v>-1.0163</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.0975</v>
+        <v>-1.0163</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.0975</v>
+        <v>-1.0163</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1026</v>
+        <v>-1.0249</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-1.1026</v>
+        <v>-1.0249</v>
       </c>
       <c r="N68" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Kyojin</t>
+          <t>mar</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.1207</v>
+        <v>-1.0934</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.5759</v>
+        <v>-0.5618</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8741</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.1207</v>
+        <v>-1.0934</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.1207</v>
+        <v>-1.0934</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.1207</v>
+        <v>-1.0934</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1417</v>
+        <v>-1.1026</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>210</v>
+        <v>104</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-1.1417</v>
+        <v>-1.1026</v>
       </c>
       <c r="N69" t="n">
-        <v>210</v>
+        <v>104</v>
       </c>
     </row>
     <row r="70">
@@ -3624,25 +3624,25 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.1398</v>
+        <v>-1.0938</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.5857</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8818</v>
+        <v>-0.8797</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.1398</v>
+        <v>-1.0938</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.1398</v>
+        <v>-1.0938</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.1398</v>
+        <v>-1.0938</v>
       </c>
       <c r="I70" t="n">
         <v>-1.1995</v>
@@ -3666,47 +3666,47 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>k1to</t>
+          <t>Kyojin</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.1425</v>
+        <v>-1.1041</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.5871</v>
+        <v>-0.5673</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8829</v>
+        <v>-0.8838</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.1425</v>
+        <v>-1.1041</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.1425</v>
+        <v>-1.1041</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.1425</v>
+        <v>-1.1041</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.1478</v>
+        <v>-1.1417</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>126</v>
+        <v>210</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.1478</v>
+        <v>-1.1417</v>
       </c>
       <c r="N71" t="n">
-        <v>126</v>
+        <v>210</v>
       </c>
     </row>
     <row r="72">
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.1715</v>
+        <v>-1.1672</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.602</v>
+        <v>-0.5998</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8946</v>
+        <v>-0.9089</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.1715</v>
+        <v>-1.1672</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.1715</v>
+        <v>-1.1672</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.1715</v>
+        <v>-1.1672</v>
       </c>
       <c r="I72" t="n">
         <v>-1.177</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.2066</v>
+        <v>-1.1931</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.62</v>
+        <v>-0.6131</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9088000000000001</v>
+        <v>-0.9192</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.2066</v>
+        <v>-1.1931</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.2066</v>
+        <v>-1.1931</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.2066</v>
+        <v>-1.1931</v>
       </c>
       <c r="I73" t="n">
         <v>-1.2235</v>
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.2593</v>
+        <v>-1.2268</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.6471</v>
+        <v>-0.6304</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9301</v>
+        <v>-0.9327</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.2593</v>
+        <v>-1.2268</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.2593</v>
+        <v>-1.2268</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.2593</v>
+        <v>-1.2268</v>
       </c>
       <c r="I74" t="n">
         <v>-1.3009</v>
@@ -3860,7 +3860,7 @@
         <v>-0.6739000000000001</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9512</v>
+        <v>-0.9664</v>
       </c>
       <c r="E75" t="n">
         <v>-1.3115</v>
@@ -3900,25 +3900,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.3743</v>
+        <v>-1.3692</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.7062</v>
+        <v>-0.7036</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.9765</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.3743</v>
+        <v>-1.3692</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.3743</v>
+        <v>-1.3692</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.3743</v>
+        <v>-1.3692</v>
       </c>
       <c r="I76" t="n">
         <v>-1.3807</v>
@@ -3946,25 +3946,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.4303</v>
+        <v>-1.425</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.735</v>
+        <v>-0.7322</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.9992</v>
+        <v>-1.0116</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.4303</v>
+        <v>-1.425</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.4303</v>
+        <v>-1.425</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.4303</v>
+        <v>-1.425</v>
       </c>
       <c r="I77" t="n">
         <v>-1.437</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.5228</v>
+        <v>-1.4779</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.7825</v>
+        <v>-0.7594</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.0365</v>
+        <v>-1.0327</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.5228</v>
+        <v>-1.4779</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.5228</v>
+        <v>-1.4779</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.5228</v>
+        <v>-1.4779</v>
       </c>
       <c r="I78" t="n">
         <v>-1.5804</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.5309</v>
+        <v>-1.5252</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.7866</v>
+        <v>-0.7837</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.0398</v>
+        <v>-1.0516</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.5309</v>
+        <v>-1.5252</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.5309</v>
+        <v>-1.5252</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.5309</v>
+        <v>-1.5252</v>
       </c>
       <c r="I79" t="n">
         <v>-1.538</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.6913</v>
+        <v>-1.685</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.8691</v>
+        <v>-0.8658</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.1046</v>
+        <v>-1.1152</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.6913</v>
+        <v>-1.685</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.6913</v>
+        <v>-1.685</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.6913</v>
+        <v>-1.685</v>
       </c>
       <c r="I80" t="n">
         <v>-1.6992</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.0033</v>
+        <v>-1.981</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.0294</v>
+        <v>-1.0179</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.2307</v>
+        <v>-1.2331</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.0033</v>
+        <v>-1.981</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.0033</v>
+        <v>-1.981</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.0033</v>
+        <v>-1.981</v>
       </c>
       <c r="I81" t="n">
         <v>-2.0314</v>
